--- a/file_upload_forms/028_sponsorship_letter_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/028_sponsorship_letter_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Uploaded Files Uploads2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Uploaded File</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Uploaded Files Uploads3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Uploaded Files Uploads4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -849,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sponsorship_letter_choices</t>
+          <t>sponsorship_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -883,10 +883,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sponsorship_letter_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>option_b</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
